--- a/pipeline_data.xlsx
+++ b/pipeline_data.xlsx
@@ -416,7 +416,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M81"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col width="31.109375" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="20.77734375" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -591,96 +591,95 @@
 Responsibilities 1: Job Responsibilites I had at Techzert AI Engineer New York, NY Nov 2024 – Present • Architected enterprise conversational AI assistants for a banking client using GPT-5, Claude, LangChain, and AWS Bedrock, integrating RAG pipelines with FAISS and Pinecone to automate Tier-1 customer support and reduce agent workload by 40%. • Engineered a credit utilization dashboard using Python, SQL, Power BI, and AWS SageMaker, integrating credit risk scoring models (Logistic Regression, Gradient Boosting) to flag at-risk accounts 1–2 reporting cycles earlier than batch reporting. • Fine-tuned BERT-based NLP models for sentiment analysis on 100K+ monthly customer feedback records, improving classification accuracy by 25% and surfacing early indicators of credit distress and collections risk. • Strengthened fraud detection systems by generating synthetic data with GenAI and deploying anomaly detection models (Isolation Forest, Autoencoders, XGBoost) on AWS SageMaker, reducing false positives by 30% across AML/KYC transaction flows. • Automated MLOps pipelines using Kubeflow, Airflow, MLflow, Docker, and Kubernetes with CI/CD/CT workflows on AWS, enabling retraining and deployment of 10+ production models while enforcing model risk management (MRM) governance.
 Responsibilities 2: Job Responsibilites I had at Deloitte Data Scientist Hyderabad, India Jun 2022 – Jul 2023 • Developed demand forecasting and customer churn models for a retail client using Python, PySpark, and Azure Databricks, applying ARIMA, LSTM, and Prophet on POS, inventory, and loyalty data to improve forecast accuracy by 20% and support merchandising and replenishment decisions. • Engineered scalable ETL pipelines on Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating multi-source retail data (transactions, store operations, customer tickets) into analytics-ready datasets and reducing data processing time by 30%. • Deployed anomaly detection models (Isolation Forest, Autoencoders) containerized with Docker and AKS, integrated with Power BI dashboards and Azure Monitor alerts to surface inventory shrinkage, sales anomalies, and store-level risks, cutting manual investigation effort by 35%.
 Skills and Action verbs which are required: Neo4j, Cypher, network topology, centrality measures, community detection, shortest-path algorithms, graph data pipelines, graph data models, fraud detection, knowledge graph development, link analysis diagrams, entity relationship charts, graph-based intelligence products, OIG, law enforcement, graph analytics, PRAC, multi-agency, multi-program, clustering, classification, anomaly detection, machine learning techniques, graph-structured data, data governance
-The Job Description: The Job Duties and Responsibilities include but are not limited to the following:   _x000D_
-_x000D_
-Develop graph-based analytic rules and models to detect fraud, waste, abuse, and mismanagement across multi-agency and multi-program datasets. _x000D_
-Apply advanced graph theory concepts—including network topology, centrality measures, community detection, and shortest-path algorithms—to identify hidden relationships and emerging fraud schemes. _x000D_
-Use Neo4j (or similar graph databases) and fluently write Cypher queries to build, test, and optimize graph models and knowledge graphs supporting PRAC analytic use cases. _x000D_
-Conduct exploratory data analysis and data profiling on public and non-public datasets to prepare graph structures and ensure high-quality ingestion. _x000D_
-Apply clustering, classification, anomaly detection, and other machine learning techniques to graph-structured data to enhance fraud detection capabilities. _x000D_
-Design, implement, and optimize graph data pipelines, schemas, and data models that support high-complexity networks and large-scale analytic environments. _x000D_
-Document methodologies, graph models, code, and analytic outputs in accordance with PRAC data governance, EDM standards, and federal oversight requirements. _x000D_
-Collaborate with PRAC stakeholders, OIG partners, and law enforcement to refine analytic approaches, validate graph-based findings, and support cross-program risk identification. _x000D_
-Conduct graph-based investigative analysis using open-source, law enforcement, and third-party data to support lead generation and case development. _x000D_
-Build link analysis diagrams, entity relationship charts, and graph-based intelligence products that visualize complex networks and relationships across multiple data sources. _x000D_
-Use graph analytics to validate PRAC-developed analytic rules and model outputs, performing due diligence to confirm or refute potential fraud indicators. _x000D_
-Support OIG and law enforcement partners by producing customized investigative work products and presenting graph-derived insights in clear, actionable formats. _x000D_
-Follow PRAC investigative workflows, templates, and policies for handling law-enforcement-sensitive data and multi-agency investigative information. _x000D_
-Evaluate emerging graph analytics tools, graph databases, and data sources; provide recommendations aligned with PRAC mission needs and federal policy. _x000D_
-Collaborate with PRAC’s OCIO, OCISO, and OCDO to configure, integrate, and optimize approved graph tools within the PRAC analytic environment. _x000D_
-Support ingestion of new data sources into graph environments, including schema design, transformation logic, and quality control. _x000D_
-Assist PRAC in analyzing cutting-edge graph-based AI/ML tools and technologies, providing technical documentation and risk considerations to support Government procurement decisions. _x000D_
-Maintain awareness of evolving fraud schemes, graph analytic techniques, and cross-program risks to inform future capability development. _x000D_
-Work closely with data scientists, investigators, statisticians, and engineers to integrate graph analytics into broader fraud detection and investigative workflows. _x000D_
-Communicate complex graph-based findings to senior PRAC leadership, OIG partners, and non-technical stakeholders in clear, accessible terms. _x000D_
-Ensure analytic integrity, reproducibility, and compliance across all graph-related workstreams. _x000D_
-Contribute to continuous improvement of analytic processes, data quality, and graph-based fraud detection methodologies._x000D_
-_x000D_
-Required Qualifications:  _x000D_
-_x000D_
-Three (3) or more years of hands-on experience using Neo4j or similar graph databases, including fluency in Cypher or comparable graph query languages. _x000D_
-Deep understanding of graph theory and network science, including network topology, centrality measures, community detection, and shortest-path algorithms. _x000D_
-Three (3) or more years of hands-on experience applying statistical and machine learning techniques—such as clustering, classifiers, and anomaly detection—to graph-structured data. _x000D_
-Three (3) or more years of experience applying graph methods to fraud detection, knowledge graph development, and identification of hidden relationships. _x000D_
-Experience designing, implementing, and optimizing graph data pipelines, graph data models, and schemas supporting high-complexity networks. _x000D_
-Strong Python programming skills, including use of standard machine learning libraries (e.g., Pandas, NumPy, Scikit-Learn, NetworkX). _x000D_
-Strong oral and written communication skills. _x000D_
-_x000D_
-Preferred Qualifications: _x000D_
-_x000D_
-Experience supporting fraud analytics, investigative support, or program integrity efforts within federal oversight environments (e.g., OIGs, PRAC, CIGIE, law enforcement). _x000D_
-Experience integrating multi-agency or multiprogram datasets into graph environments to detect cross-program risks and complex fraud schemes. _x000D_
-Experience producing graph-based investigative work products such as link analysis diagrams, entity relationship charts, and network visualizations. _x000D_
-Experience developing or deploying AI/ML models applied to graph data. _x000D_
-Experience supporting enterprise data management (EDM), data governance, and federal data quality standards. _x000D_
-Familiarity with PRAC AI governance policies, OMB memoranda (M-25-22, M-25-21, M-26-04), and the NIST AI Risk Management Framework. _x000D_
+The Job Description: The Job Duties and Responsibilities include but are not limited to the following:   _x000D_
+_x000D_
+Develop graph-based analytic rules and models to detect fraud, waste, abuse, and mismanagement across multi-agency and multi-program datasets. _x000D_
+Apply advanced graph theory concepts—including network topology, centrality measures, community detection, and shortest-path algorithms—to identify hidden relationships and emerging fraud schemes. _x000D_
+Use Neo4j (or similar graph databases) and fluently write Cypher queries to build, test, and optimize graph models and knowledge graphs supporting PRAC analytic use cases. _x000D_
+Conduct exploratory data analysis and data profiling on public and non-public datasets to prepare graph structures and ensure high-quality ingestion. _x000D_
+Apply clustering, classification, anomaly detection, and other machine learning techniques to graph-structured data to enhance fraud detection capabilities. _x000D_
+Design, implement, and optimize graph data pipelines, schemas, and data models that support high-complexity networks and large-scale analytic environments. _x000D_
+Document methodologies, graph models, code, and analytic outputs in accordance with PRAC data governance, EDM standards, and federal oversight requirements. _x000D_
+Collaborate with PRAC stakeholders, OIG partners, and law enforcement to refine analytic approaches, validate graph-based findings, and support cross-program risk identification. _x000D_
+Conduct graph-based investigative analysis using open-source, law enforcement, and third-party data to support lead generation and case development. _x000D_
+Build link analysis diagrams, entity relationship charts, and graph-based intelligence products that visualize complex networks and relationships across multiple data sources. _x000D_
+Use graph analytics to validate PRAC-developed analytic rules and model outputs, performing due diligence to confirm or refute potential fraud indicators. _x000D_
+Support OIG and law enforcement partners by producing customized investigative work products and presenting graph-derived insights in clear, actionable formats. _x000D_
+Follow PRAC investigative workflows, templates, and policies for handling law-enforcement-sensitive data and multi-agency investigative information. _x000D_
+Evaluate emerging graph analytics tools, graph databases, and data sources; provide recommendations aligned with PRAC mission needs and federal policy. _x000D_
+Collaborate with PRAC’s OCIO, OCISO, and OCDO to configure, integrate, and optimize approved graph tools within the PRAC analytic environment. _x000D_
+Support ingestion of new data sources into graph environments, including schema design, transformation logic, and quality control. _x000D_
+Assist PRAC in analyzing cutting-edge graph-based AI/ML tools and technologies, providing technical documentation and risk considerations to support Government procurement decisions. _x000D_
+Maintain awareness of evolving fraud schemes, graph analytic techniques, and cross-program risks to inform future capability development. _x000D_
+Work closely with data scientists, investigators, statisticians, and engineers to integrate graph analytics into broader fraud detection and investigative workflows. _x000D_
+Communicate complex graph-based findings to senior PRAC leadership, OIG partners, and non-technical stakeholders in clear, accessible terms. _x000D_
+Ensure analytic integrity, reproducibility, and compliance across all graph-related workstreams. _x000D_
+Contribute to continuous improvement of analytic processes, data quality, and graph-based fraud detection methodologies._x000D_
+_x000D_
+Required Qualifications:  _x000D_
+_x000D_
+Three (3) or more years of hands-on experience using Neo4j or similar graph databases, including fluency in Cypher or comparable graph query languages. _x000D_
+Deep understanding of graph theory and network science, including network topology, centrality measures, community detection, and shortest-path algorithms. _x000D_
+Three (3) or more years of hands-on experience applying statistical and machine learning techniques—such as clustering, classifiers, and anomaly detection—to graph-structured data. _x000D_
+Three (3) or more years of experience applying graph methods to fraud detection, knowledge graph development, and identification of hidden relationships. _x000D_
+Experience designing, implementing, and optimizing graph data pipelines, graph data models, and schemas supporting high-complexity networks. _x000D_
+Strong Python programming skills, including use of standard machine learning libraries (e.g., Pandas, NumPy, Scikit-Learn, NetworkX). _x000D_
+Strong oral and written communication skills. _x000D_
+_x000D_
+Preferred Qualifications: _x000D_
+_x000D_
+Experience supporting fraud analytics, investigative support, or program integrity efforts within federal oversight environments (e.g., OIGs, PRAC, CIGIE, law enforcement). _x000D_
+Experience integrating multi-agency or multiprogram datasets into graph environments to detect cross-program risks and complex fraud schemes. _x000D_
+Experience producing graph-based investigative work products such as link analysis diagrams, entity relationship charts, and network visualizations. _x000D_
+Experience developing or deploying AI/ML models applied to graph data. _x000D_
+Experience supporting enterprise data management (EDM), data governance, and federal data quality standards. _x000D_
+Familiarity with PRAC AI governance policies, OMB memoranda (M-25-22, M-25-21, M-26-04), and the NIST AI Risk Management Framework. _x000D_
 Advanced certifications in data science, graph analytics, or fraud examination (e.g., CFE, Neo4j Certified Professional)."</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>ChatGPT said:
-Professional Summary
+Professional Summary — Data Scientist
 Writing
-Data Scientist specializing in **graph analytics**, **fraud detection**, and **machine learning** to identify hidden relationships, anomalous patterns, and cross-program risks across complex datasets. Experienced in building scalable **graph data pipelines**, **knowledge graphs**, and cloud-based analytical solutions to improve investigative efficiency and data quality. Applied **Python**, **Neo4j**, **Cypher**, and advanced graph theory techniques to support relationship discovery, risk assessment, and actionable intelligence. Focused on **data governance**, model integrity, reproducible analytics, and clear communication of technical findings to business and investigative stakeholders.
-Responsibilities 1: Techzert AI Engineer | New York, NY
-Nov 2024 – Present
-Architected scalable **Neo4j** knowledge graphs using **Cypher**, **Python**, and **NetworkX** to connect financial entities and transactions across **multi-program** datasets, uncovering hidden relationships and improving fraud investigation efficiency by 35%.
-Computed **network topology**, **centrality measures**, **community detection**, and **shortest-path algorithms** to identify suspicious transaction networks, emerging fraud schemes, and high-risk entities, accelerating investigative lead generation by 30%.
-Engineered **graph data pipelines**, **graph data models**, schemas, and ingestion workflows using **Pandas** and **NumPy**, profiling public and non-public datasets and improving data quality and relationship-matching accuracy by 25%.
-Applied **clustering**, **classification**, **anomaly detection**, and other **machine learning techniques** to **graph-structured data** for **fraud detection**, waste, abuse, and mismanagement analysis, reducing false-positive alerts by 30%.
-Managed **graph analytics**, **knowledge graph development**, and **data governance** documentation; troubleshot query performance, modified analytic rules, monitored model outputs, corrected data inconsistencies, and participated in stakeholder reviews to validate findings and improve investigative workflows by 25%.
-Responsibilities 2: Deloitte Data Scientist | Hyderabad, India
-Jun 2022 – Jul 2023
-Designed and optimized **graph-based intelligence products** using **Python**, **Scikit-learn**, and **SQL** to analyze interconnected retail, financial, and operational records, identifying suspicious entity relationships and improving risk detection coverage by 28%.
-Conducted exploratory data analysis and **data profiling** across **multi-agency** and **multi-program** datasets, integrating structured and third-party information into graph-ready formats and reducing data preparation time by 30%.
-Generated **link analysis diagrams**, **entity relationship charts**, and **network visualizations** using **Tableau** and **Matplotlib**, presenting complex relationships and investigative insights in accessible formats that improved analyst review efficiency by 35%.
-Supported **PRAC**, **OIG**, **law enforcement**, and **multi-agency** investigative use cases by documenting analytic methodologies, validating fraud indicators, and aligning work products with **EDM standards**, federal data quality requirements, and **data governance** policies; oriented stakeholders to review procedures and investigative workflows.
-Evaluated emerging **graph analytics tools**, **AI/ML technologies**, and data sources; contributed technical documentation and risk assessments aligned with the **NIST AI Risk Management Framework**, **OMB M-25-22**, **OMB M-25-21**, and **OMB M-26-04**, motivating continuous improvement that increased analytic reproducibility by 25%.
-Important accuracy note: These bullets incorporate the requested job-description keywords, including federal investigative terminology and graph technologies. Keep claims about **Neo4j**, **Cypher**, **PRAC**/**OIG** collaboration, federal standards, and the quantified achievements only if you can substantiate them in an interview. The job description also mentions CIGIE, OCIO, OCISO, OCDO, and certifications such as CFE and **Neo4j** Certified Professional; these are better listed as experience or credentials only if applicable, rather than presented as qualifications you already hold.</t>
+Data Scientist specializing in **graph analytics**, **machine learning**, and **fraud detection** to identify hidden relationships, suspicious networks, and cross-program risks across complex datasets. Experienced in building scalable **Python** analytics solutions, **Neo4j** knowledge graphs, and **graph-based intelligence products** to improve investigative efficiency and data quality. Skilled in **network topology**, **centrality measures**, **community detection**, **Cypher**, and **anomaly detection** for identifying fraud, waste, abuse, and mismanagement. Focused on **data governance**, reproducible analytics, and actionable insights that strengthen risk assessment, program integrity, and investigative decision-making. Adept at collaborating with technical teams and non-technical stakeholders to communicate complex findings clearly.
+Responsibilities 1 — Techzert AI Engineer | New York, NY
+Architected **Neo4j** knowledge graphs using **Cypher**, **Python**, and **NetworkX** to map banking entities, transactions, and relationships across 5+ data sources, supporting graph-based **fraud detection** and hidden relationship discovery.
+Applied **network topology**, **centrality measures**, **community detection**, and **shortest-path algorithms** to identify suspicious transaction networks, uncover emerging fraud schemes, and prioritize high-risk entities across **multi-program** datasets.
+Conducted exploratory data analysis and data profiling with **Pandas** and **NumPy**, correcting data inconsistencies and optimizing **graph data pipelines**, schemas, and **graph data models** to improve ingestion quality by 30%.
+Applied **Scikit-learn** **clustering**, **classification**, and **anomaly detection** techniques to **graph-structured data**, improving suspicious-activity identification by 25% and validating analytic rules through investigative due diligence.
+Managed **data governance**, model documentation, and reproducibility standards while producing **link analysis diagrams**, **entity relationship charts**, and **graph-based intelligence products**; participated in stakeholder reviews and communicated actionable findings to investigative teams.
+Responsibilities 2 — Deloitte Data Scientist | Hyderabad, India
+Designed **graph data models** and **knowledge graph development** workflows using **Python**, **SQL**, and **Apache Spark**, integrating 10+ public, non-public, and third-party datasets to expose cross-program relationships and improve investigative lead generation by 30%.
+Computed relationship patterns and network connectivity measures using **graph analytics** and graph query techniques, supporting **multi-agency** risk identification and the investigation of fraud, waste, abuse, and mismanagement.
+Troubleshot and modified graph ingestion workflows, data transformations, and schema validation rules, reducing data-quality exceptions by 35% and strengthening enterprise data management (EDM) and federal data quality compliance.
+Collaborated with **PRAC** stakeholders, **OIG** partners, **law enforcement**, investigators, statisticians, and engineers to validate graph-derived findings, refine analytic approaches, and support case development across complex investigative workflows.
+Evaluated emerging **graph analytics** and graph-based AI/ML tools, documented technical methodologies and risk considerations, and prepared customized investigative work products aligned with **PRAC**, **CIGIE**, **NIST AI Risk Management Framework**, and applicable **OMB M-25-22, M-25-21, and M-26-04** guidance.
+Important before using this résumé: The job description requires at least three years of hands-on graph database and graph-ML experience. These bullets include the target keywords, but keep only tools, responsibilities, standards, and achievements you can substantiate in an interview. **PRAC**, **OIG**, CIGIE, law-enforcement collaboration, and federal compliance experience should not be represented as direct experience unless you actually performed that work.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Data Scientist specializing in **graph analytics**, **fraud detection**, and **machine learning** to identify hidden relationships, anomalous patterns, and cross-program risks across complex datasets. Experienced in building scalable **graph data pipelines**, **knowledge graphs**, and cloud-based analytical solutions to improve investigative efficiency and data quality. Applied **Python**, **Neo4j**, **Cypher**, and advanced graph theory techniques to support relationship discovery, risk assessment, and actionable intelligence. Focused on **data governance**, model integrity, reproducible analytics, and clear communication of technical findings to business and investigative stakeholders.</t>
+          <t>Data Scientist specializing in **graph analytics**, **machine learning**, and **fraud detection** to identify hidden relationships, suspicious networks, and cross-program risks across complex datasets. Experienced in building scalable **Python** analytics solutions, **Neo4j** knowledge graphs, and **graph-based intelligence products** to improve investigative efficiency and data quality. Skilled in **network topology**, **centrality measures**, **community detection**, **Cypher**, and **anomaly detection** for identifying fraud, waste, abuse, and mismanagement. Focused on **data governance**, reproducible analytics, and actionable insights that strengthen risk assessment, program integrity, and investigative decision-making. Adept at collaborating with technical teams and non-technical stakeholders to communicate complex findings clearly.</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>Architected scalable **Neo4j** knowledge graphs using **Cypher**, **Python**, and **NetworkX** to connect financial entities and transactions across multi-program datasets, uncovering hidden relationships and improving fraud investigation efficiency by 35%.
-Computed **network topology**, **centrality measures**, **community detection**, and **shortest-path algorithms** to identify suspicious transaction networks, emerging fraud schemes, and high-risk entities, accelerating investigative lead generation by 30%.
-Engineered **graph data pipelines**, **graph data models**, schemas, and ingestion workflows using **Pandas** and **NumPy**, profiling public and non-public datasets and improving data quality and relationship-matching accuracy by 25%.
-Applied **clustering**, **classification**, **anomaly detection**, and other **machine learning techniques** to graph-structured data for **fraud detection**, waste, abuse, and mismanagement analysis, reducing false-positive alerts by 30%.
-Managed **graph analytics**, **knowledge graph development**, and **data governance** documentation; troubleshot query performance, modified analytic rules, monitored model outputs, corrected data inconsistencies, and participated in stakeholder reviews to validate findings and improve investigative workflows by 25%.</t>
+          <t>Architected **Neo4j** knowledge graphs using **Cypher**, **Python**, and **NetworkX** to map banking entities, transactions, and relationships across 5+ data sources, supporting graph-based **fraud detection** and hidden relationship discovery.
+Applied **network topology**, **centrality measures**, **community detection**, and **shortest-path algorithms** to identify suspicious transaction networks, uncover emerging fraud schemes, and prioritize high-risk entities across **multi-program** datasets.
+Conducted exploratory data analysis and data profiling with **Pandas** and **NumPy**, correcting data inconsistencies and optimizing **graph data pipelines**, schemas, and **graph data models** to improve ingestion quality by 30%.
+Applied **Scikit-learn** **clustering**, **classification**, and **anomaly detection** techniques to **graph-structured data**, improving suspicious-activity identification by 25% and validating analytic rules through investigative due diligence.
+Managed **data governance**, model documentation, and reproducibility standards while producing **link analysis diagrams**, **entity relationship charts**, and **graph-based intelligence products**; participated in stakeholder reviews and communicated actionable findings to investigative teams.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Designed and optimized **graph-based intelligence products** using **Python**, **Scikit-learn**, and **SQL** to analyze interconnected retail, financial, and operational records, identifying suspicious entity relationships and improving risk detection coverage by 28%.
-Conducted exploratory data analysis and **data profiling** across multi-agency and multi-program datasets, integrating structured and third-party information into graph-ready formats and reducing data preparation time by 30%.
-Generated **link analysis diagrams**, **entity relationship charts**, and **network visualizations** using **Tableau** and **Matplotlib**, presenting complex relationships and investigative insights in accessible formats that improved analyst review efficiency by 35%.
-Supported **PRAC**, **OIG**, **law enforcement**, and **multi-agency** investigative use cases by documenting analytic methodologies, validating fraud indicators, and aligning work products with **EDM standards**, federal data quality requirements, and **data governance** policies; oriented stakeholders to review procedures and investigative workflows.
-Evaluated emerging **graph analytics tools**, **AI/ML technologies**, and data sources; contributed technical documentation and risk assessments aligned with the **NIST AI Risk Management Framework**, **OMB M-25-22**, **OMB M-25-21**, and **OMB M-26-04**, motivating continuous improvement that increased analytic reproducibility by 25%.</t>
+          <t>Designed **graph data models** and **knowledge graph development** workflows using **Python**, **SQL**, and **Apache Spark**, integrating 10+ public, non-public, and third-party datasets to expose cross-program relationships and improve investigative lead generation by 30%.
+Computed relationship patterns and network connectivity measures using **graph analytics** and graph query techniques, supporting **multi-agency** risk identification and the investigation of fraud, waste, abuse, and mismanagement.
+Troubleshot and modified graph ingestion workflows, data transformations, and schema validation rules, reducing data-quality exceptions by 35% and strengthening enterprise data management (EDM) and federal data quality compliance.
+Collaborated with **PRAC** stakeholders, **OIG** partners, **law enforcement**, investigators, statisticians, and engineers to validate graph-derived findings, refine analytic approaches, and support case development across complex investigative workflows.
+Evaluated emerging **graph analytics** and graph-based AI/ML tools, documented technical methodologies and risk considerations, and prepared customized investigative work products aligned with **PRAC**, **CIGIE**, **NIST AI Risk Management Framework**, and applicable **OMB M-25-22, M-25-21, and M-26-04** guidance.
+Important before using this résumé: The job description requires at least three years of hands-on graph database and graph-ML experience. These bullets include the target keywords, but keep only tools, responsibilities, standards, and achievements you can substantiate in an interview. **PRAC**, **OIG**, CIGIE, law-enforcement collaboration, and federal compliance experience should not be represented as direct experience unless you actually performed that work.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -774,22 +773,22 @@
 Responsibilities 1: Job Responsibilites I had at Techzert AI Engineer New York, NY Nov 2024 – Present • Architected enterprise conversational AI assistants for a banking client using GPT-5, Claude, LangChain, and AWS Bedrock, integrating RAG pipelines with FAISS and Pinecone to automate Tier-1 customer support and reduce agent workload by 40%. • Engineered a credit utilization dashboard using Python, SQL, Power BI, and AWS SageMaker, integrating credit risk scoring models (Logistic Regression, Gradient Boosting) to flag at-risk accounts 1–2 reporting cycles earlier than batch reporting. • Fine-tuned BERT-based NLP models for sentiment analysis on 100K+ monthly customer feedback records, improving classification accuracy by 25% and surfacing early indicators of credit distress and collections risk. • Strengthened fraud detection systems by generating synthetic data with GenAI and deploying anomaly detection models (Isolation Forest, Autoencoders, XGBoost) on AWS SageMaker, reducing false positives by 30% across AML/KYC transaction flows. • Automated MLOps pipelines using Kubeflow, Airflow, MLflow, Docker, and Kubernetes with CI/CD/CT workflows on AWS, enabling retraining and deployment of 10+ production models while enforcing model risk management (MRM) governance.
 Responsibilities 2: Job Responsibilites I had at Deloitte Data Scientist Hyderabad, India Jun 2022 – Jul 2023 • Developed demand forecasting and customer churn models for a retail client using Python, PySpark, and Azure Databricks, applying ARIMA, LSTM, and Prophet on POS, inventory, and loyalty data to improve forecast accuracy by 20% and support merchandising and replenishment decisions. • Engineered scalable ETL pipelines on Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating multi-source retail data (transactions, store operations, customer tickets) into analytics-ready datasets and reducing data processing time by 30%. • Deployed anomaly detection models (Isolation Forest, Autoencoders) containerized with Docker and AKS, integrated with Power BI dashboards and Azure Monitor alerts to surface inventory shrinkage, sales anomalies, and store-level risks, cutting manual investigation effort by 35%.
 Skills and Action verbs which are required: Python, data analysis tools, external and public data sources, AI tools, policy developments, regulatory landscape, paid media, public-affairs campaigns, policy implementation, applied causal inference, quasi-experimental designs, difference-in-differences, regression discontinuity, synthetic control, instrumental variables, observational data, technical fluency, hands-on data science experience, policy, government affairs, regulatory team, investor-relations, financial-disclosure data standards, ambiguous, fast-moving environments
-The Job Description: Key responsibilities_x000D_
-Partner with product and business teams across the company to produce supporting analyses and data collateral for specific policy position papers and partnership conversations_x000D_
-Determine which metrics faithfully represent our company to legislators, regulators, and the public_x000D_
-Own the dashboards and pipelines that keep externally-shared numbers consistent, so the Policy team can move quickly without creating discrepancies_x000D_
-Use AI tools to aggregate news, policy developments, and other public data sources to track trends and provide a clear picture of the evolving regulatory landscape_x000D_
-Develop measurement frameworks for policy communications, paid media, and public-affairs campaigns_x000D_
-Design and implement policy analyses to support internal position development or measure the impact of policy implementation for external audiences_x000D_
-Minimum qualifications_x000D_
-Proficiency in Python, SQL, and data analysis tools, with experience working with external and public data sources_x000D_
-Experience producing analysis that reaches external audiences such as policy, communications, investor relations, public affairs, or published research_x000D_
-Applied causal inference using quasi-experimental designs (e.g., difference-in-differences, regression discontinuity, synthetic control, instrumental variables, or matching) to measure policy or program impact from observational data_x000D_
-Demonstrated ability to translate complex analyses into clear, actionable recommendations for audiences with differing levels of technical fluency_x000D_
-Preferred qualifications_x000D_
-6+ years of hands-on data science experience_x000D_
-Direct experience supporting a policy, government affairs, or regulatory team with data and analysis_x000D_
-Familiarity with investor-relations or financial-disclosure data standards and the consistency requirements they entail_x000D_
+The Job Description: Key responsibilities_x000D_
+Partner with product and business teams across the company to produce supporting analyses and data collateral for specific policy position papers and partnership conversations_x000D_
+Determine which metrics faithfully represent our company to legislators, regulators, and the public_x000D_
+Own the dashboards and pipelines that keep externally-shared numbers consistent, so the Policy team can move quickly without creating discrepancies_x000D_
+Use AI tools to aggregate news, policy developments, and other public data sources to track trends and provide a clear picture of the evolving regulatory landscape_x000D_
+Develop measurement frameworks for policy communications, paid media, and public-affairs campaigns_x000D_
+Design and implement policy analyses to support internal position development or measure the impact of policy implementation for external audiences_x000D_
+Minimum qualifications_x000D_
+Proficiency in Python, SQL, and data analysis tools, with experience working with external and public data sources_x000D_
+Experience producing analysis that reaches external audiences such as policy, communications, investor relations, public affairs, or published research_x000D_
+Applied causal inference using quasi-experimental designs (e.g., difference-in-differences, regression discontinuity, synthetic control, instrumental variables, or matching) to measure policy or program impact from observational data_x000D_
+Demonstrated ability to translate complex analyses into clear, actionable recommendations for audiences with differing levels of technical fluency_x000D_
+Preferred qualifications_x000D_
+6+ years of hands-on data science experience_x000D_
+Direct experience supporting a policy, government affairs, or regulatory team with data and analysis_x000D_
+Familiarity with investor-relations or financial-disclosure data standards and the consistency requirements they entail_x000D_
 Comfort operating in ambiguous, fast-moving environments where creating clarity and driving progress is part of the role"</t>
         </is>
       </c>
@@ -798,46 +797,44 @@
           <t>ChatGPT said:
 Professional Summary
 Writing
-Data Scientist with expertise in **Python**, **SQL**, **causal inference**, and **data analysis tools** to transform complex datasets into actionable business and **policy** insights. Experienced in building **scalable data pipelines**, measurement frameworks, and dashboards that maintain consistent reporting across internal and external audiences. Applied **quasi-experimental designs**, regression analysis, and **observational data** to evaluate program effectiveness, identify trends, and support evidence-based decisions. Skilled in leveraging **AI tools** and public data sources to monitor regulatory developments, assess emerging risks, and communicate findings to technical and nontechnical stakeholders. Delivered measurable improvements in operational efficiency, analytical accuracy, and risk management across financial and business environments.
-Responsibilities 1 — Techzert AI Engineer | New York, NY
-Nov 2024 – Present
-Partnered with product, business, and **policy**-facing stakeholders to analyze financial and **external and public data sources** using **Python**, **SQL**, and **data analysis tools**, producing evidence-based data collateral for **policy** position papers, partnership discussions, and external communications while improving reporting efficiency by 35%.
-Managed executive dashboards and data pipelines using **Power BI**, **AWS Redshift**, and **AWS Glue**, established consistent metrics for legislators, regulators, and public audiences, and aligned reporting with **investor-relations** requirements and **financial-disclosure data standards**, reducing reporting discrepancies by 30%.
-Aggregated news, **policy developments**, and public information through **AI tools**, **LangChain**, and **AWS Bedrock** to monitor trends and interpret the evolving **regulatory landscape**, delivering timely insights that shortened research turnaround by 40%.
-Designed **measurement frameworks** for **paid media**, **public-affairs campaigns**, and **policy** communications, computed campaign performance metrics, and applied **difference-in-differences**, **regression discontinuity**, and **synthetic control** methods to evaluate the impact of **policy implementation**, improving impact assessment accuracy by 25%.
-Conducted **applied causal inference** using **observational data**, **instrumental variables**, and matching techniques to evaluate **policy**-related outcomes; translated **ambiguous** findings into actionable recommendations, troubleshot data inconsistencies, corrected reporting gaps, and motivated cross-functional teams to make evidence-based decisions in **fast-moving environments**.
-Responsibilities 2 — Deloitte Data Scientist | Hyderabad, India
-Jun 2022 – Jul 2023
-Analyzed customer, transaction, and market datasets using **Python**, **R**, and **Pandas**, incorporating **external and public data sources** to identify emerging business trends and support research-backed recommendations, improving analytical accuracy by 20%.
-Engineered scalable data integration workflows with **Azure Data Factory**, **Azure Data Lake Storage Gen2**, and **Azure Synapse Analytics**, standardizing published metrics and audit-ready datasets to reduce data preparation time by 30% and support reliable external reporting.
-Participated in cross-functional reviews with business, communications, and regulatory stakeholders, oriented nontechnical audiences to complex analytical findings, and presented clear recommendations that strengthened decision-making and improved stakeholder understanding by 25%.
-Evaluated **policy** and program outcomes using **quasi-experimental designs**, **propensity score matching**, and **regression analysis** on observational datasets; modified analytical approaches to address confounding factors and measured intervention effectiveness, improving outcome assessments by 20%.
-Monitored data quality and reporting controls through **Tableau**, **Azure Monitor**, and **SQL**, troubleshot pipeline failures, corrected metric inconsistencies, and managed competing priorities in **ambiguous**, **fast-moving environments**, reducing manual reporting and investigation effort by 35%.
-Important: The job description requests 6+ years of **hands-on data science experience** and direct **policy**, **government affairs**, or regulatory-team exposure. These drafts incorporate the requested ATS terminology, but the added tools, methods, responsibilities, and metrics should be retained in your résumé only if you can substantiate them in an interview. Your listed employment dates alone do not establish six years of experience.</t>
+Data Scientist specializing in **Python**, **SQL**, and **causal inference** to deliver actionable insights for **policy** decisions, public affairs, and business strategy. Experienced in building **scalable data pipelines**, **cloud-native analytics solutions**, and dashboards that maintain consistent, reliable metrics for external reporting. Applied **quasi-experimental designs**, including **difference-in-differences**, **regression discontinuity**, **synthetic control**, and **instrumental variables**, to evaluate **policy** and program impacts. Leveraged **AI tools**, public data sources, and regulatory trend analysis to strengthen measurement frameworks, assess risks, and improve decision-making. Translated complex analyses into clear recommendations for technical and nontechnical stakeholders in **ambiguous**, **fast-moving environments**.
+Responsibilities 1 — Techzert AI Engineer
+Partnered with product, business, and **policy**-facing teams to produce data analyses and supporting materials for **policy** position papers and partnership discussions, using **Python**, **SQL**, and **Pandas** to evaluate financial and operational trends and improve reporting efficiency by 40%.
+Managed externally shared dashboards and data pipelines using **Power BI**, **AWS Redshift**, and **AWS Glue**, establishing consistent metrics and validation checks that reduced reporting discrepancies by 30% and supported accurate communications with legislators, regulators, and public audiences.
+Aggregated news, **policy developments**, regulatory updates, and **external and public data sources** using **AI tools**, **LangChain**, and **AWS Bedrock**, identifying emerging trends and improving **regulatory landscape** monitoring coverage by 35%.
+Designed **applied causal inference** studies using **difference-in-differences**, **regression discontinuity**, **synthetic control**, and **instrumental variables** to assess **policy implementation** and program impact from **observational data**, evaluating outcomes across 100K+ records and producing evidence-based recommendations.
+Developed measurement frameworks for **policy communications**, **paid media**, and **public-affairs campaigns** using **SQL**, **Amazon S3**, and **AWS Lambda**, computed campaign performance metrics, and translated complex findings into actionable recommendations for **policy**, communications, **government affairs**, and **investor-relations** stakeholders, improving evaluation turnaround by 25%.
+Responsibilities 2 — Deloitte Data Scientist
+Conducted **data analysis** using **R**, **PySpark**, and **Azure Databricks** to assess public datasets, business indicators, and **observational data**, identifying trends that supported **policy** research and improved forecast accuracy by 20%.
+Engineered reliable reporting pipelines with **Azure Data Factory**, **ADLS Gen2**, and **Azure Synapse Analytics**, consolidating multiple external data sources and applying **financial-disclosure data standards** and consistency controls to reduce data processing time by 30%.
+Applied **quasi-experimental designs** and **matching methods** to compare program outcomes, troubleshoot analytical gaps, and evaluate **policy**-related changes; modified analytical models and corrected data-quality issues to improve measurement reliability by 25%.
+Monitored public-affairs and regulatory performance indicators through **Tableau**, **Azure Monitor**, and **Excel**, participated in cross-functional reviews, and oriented stakeholders with differing levels of **technical fluency** toward clear, evidence-based recommendations, reducing manual investigation effort by 35%.
+Managed analytical deliverables in **Git**, **Jira**, and **Agile/Scrum** workflows, motivated cross-functional teams to resolve **ambiguous** requirements, and supported **policy**, **government affairs**, and regulatory stakeholders in **fast-moving environments**, improving reporting readiness by 30%.
+Important: The target description requires experience with causal inference, **policy** or regulatory teams, external-facing analysis, and financial-disclosure standards. These drafts incorporate those keywords, but you should retain claims about specific methods, tools, and measurable outcomes only if you can substantiate them in an interview.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Data Scientist with expertise in **Python**, **SQL**, **causal inference**, and **data analysis tools** to transform complex datasets into actionable business and policy insights. Experienced in building **scalable data pipelines**, measurement frameworks, and dashboards that maintain consistent reporting across internal and external audiences. Applied **quasi-experimental designs**, regression analysis, and observational data to evaluate program effectiveness, identify trends, and support evidence-based decisions. Skilled in leveraging **AI tools** and public data sources to monitor regulatory developments, assess emerging risks, and communicate findings to technical and nontechnical stakeholders. Delivered measurable improvements in operational efficiency, analytical accuracy, and risk management across financial and business environments.</t>
+          <t>Data Scientist specializing in **Python**, **SQL**, and **causal inference** to deliver actionable insights for **policy** decisions, public affairs, and business strategy. Experienced in building **scalable data pipelines**, **cloud-native analytics solutions**, and dashboards that maintain consistent, reliable metrics for external reporting. Applied **quasi-experimental designs**, including **difference-in-differences**, **regression discontinuity**, **synthetic control**, and **instrumental variables**, to evaluate **policy** and program impacts. Leveraged **AI tools**, public data sources, and regulatory trend analysis to strengthen measurement frameworks, assess risks, and improve decision-making. Translated complex analyses into clear recommendations for technical and nontechnical stakeholders in **ambiguous**, **fast-moving environments**.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Partnered with product, business, and policy-facing stakeholders to analyze financial and **external and public data sources** using **Python**, **SQL**, and **data analysis tools**, producing evidence-based data collateral for policy position papers, partnership discussions, and external communications while improving reporting efficiency by 35%.
-Managed executive dashboards and data pipelines using **Power BI**, **AWS Redshift**, and **AWS Glue**, established consistent metrics for legislators, regulators, and public audiences, and aligned reporting with **investor-relations** requirements and **financial-disclosure data standards**, reducing reporting discrepancies by 30%.
-Aggregated news, **policy developments**, and public information through **AI tools**, **LangChain**, and **AWS Bedrock** to monitor trends and interpret the evolving **regulatory landscape**, delivering timely insights that shortened research turnaround by 40%.
-Designed **measurement frameworks** for **paid media**, **public-affairs campaigns**, and policy communications, computed campaign performance metrics, and applied **difference-in-differences**, **regression discontinuity**, and **synthetic control** methods to evaluate the impact of **policy implementation**, improving impact assessment accuracy by 25%.
-Conducted **applied causal inference** using **observational data**, **instrumental variables**, and matching techniques to evaluate policy-related outcomes; translated ambiguous findings into actionable recommendations, troubleshot data inconsistencies, corrected reporting gaps, and motivated cross-functional teams to make evidence-based decisions in fast-moving environments.</t>
+          <t>Partnered with product, business, and **policy**-facing teams to produce data analyses and supporting materials for **policy** position papers and partnership discussions, using **Python**, **SQL**, and **Pandas** to evaluate financial and operational trends and improve reporting efficiency by 40%.
+Managed externally shared dashboards and data pipelines using **Power BI**, **AWS Redshift**, and **AWS Glue**, establishing consistent metrics and validation checks that reduced reporting discrepancies by 30% and supported accurate communications with legislators, regulators, and public audiences.
+Aggregated news, **policy developments**, regulatory updates, and **external and public data sources** using **AI tools**, **LangChain**, and **AWS Bedrock**, identifying emerging trends and improving **regulatory landscape** monitoring coverage by 35%.
+Designed **applied causal inference** studies using **difference-in-differences**, **regression discontinuity**, **synthetic control**, and **instrumental variables** to assess **policy implementation** and program impact from **observational data**, evaluating outcomes across 100K+ records and producing evidence-based recommendations.
+Developed measurement frameworks for **policy communications**, **paid media**, and **public-affairs campaigns** using **SQL**, **Amazon S3**, and **AWS Lambda**, computed campaign performance metrics, and translated complex findings into actionable recommendations for **policy**, communications, **government affairs**, and **investor-relations** stakeholders, improving evaluation turnaround by 25%.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Analyzed customer, transaction, and market datasets using **Python**, **R**, and **Pandas**, incorporating **external and public data sources** to identify emerging business trends and support research-backed recommendations, improving analytical accuracy by 20%.
-Engineered scalable data integration workflows with **Azure Data Factory**, **Azure Data Lake Storage Gen2**, and **Azure Synapse Analytics**, standardizing published metrics and audit-ready datasets to reduce data preparation time by 30% and support reliable external reporting.
-Participated in cross-functional reviews with business, communications, and regulatory stakeholders, oriented nontechnical audiences to complex analytical findings, and presented clear recommendations that strengthened decision-making and improved stakeholder understanding by 25%.
-Evaluated policy and program outcomes using **quasi-experimental designs**, **propensity score matching**, and **regression analysis** on observational datasets; modified analytical approaches to address confounding factors and measured intervention effectiveness, improving outcome assessments by 20%.
-Monitored data quality and reporting controls through **Tableau**, **Azure Monitor**, and **SQL**, troubleshot pipeline failures, corrected metric inconsistencies, and managed competing priorities in ambiguous, fast-moving environments, reducing manual reporting and investigation effort by 35%.
-Important: The job description requests 6+ years of hands-on data science experience and direct policy, government affairs, or regulatory-team exposure. These drafts incorporate the requested ATS terminology, but the added tools, methods, responsibilities, and metrics should be retained in your résumé only if you can substantiate them in an interview. Your listed employment dates alone do not establish six years of experience.</t>
+          <t>Conducted **data analysis** using **R**, **PySpark**, and **Azure Databricks** to assess public datasets, business indicators, and **observational data**, identifying trends that supported **policy** research and improved forecast accuracy by 20%.
+Engineered reliable reporting pipelines with **Azure Data Factory**, **ADLS Gen2**, and **Azure Synapse Analytics**, consolidating multiple external data sources and applying **financial-disclosure data standards** and consistency controls to reduce data processing time by 30%.
+Applied **quasi-experimental designs** and **matching methods** to compare program outcomes, troubleshoot analytical gaps, and evaluate **policy**-related changes; modified analytical models and corrected data-quality issues to improve measurement reliability by 25%.
+Monitored public-affairs and regulatory performance indicators through **Tableau**, **Azure Monitor**, and **Excel**, participated in cross-functional reviews, and oriented stakeholders with differing levels of **technical fluency** toward clear, evidence-based recommendations, reducing manual investigation effort by 35%.
+Managed analytical deliverables in **Git**, **Jira**, and **Agile/Scrum** workflows, motivated cross-functional teams to resolve **ambiguous** requirements, and supported **policy**, **government affairs**, and regulatory stakeholders in **fast-moving environments**, improving reporting readiness by 30%.
+Important: The target description requires experience with causal inference, **policy** or regulatory teams, external-facing analysis, and financial-disclosure standards. These drafts incorporate those keywords, but you should retain claims about specific methods, tools, and measurable outcomes only if you can substantiate them in an interview.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1032,7 +1029,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1199,7 +1196,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1406,7 +1403,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1567,7 +1564,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1730,7 +1727,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1946,7 +1943,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -2169,7 +2166,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -2334,7 +2331,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -2532,7 +2529,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2688,7 +2685,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2859,7 +2856,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -3066,7 +3063,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -3231,7 +3228,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -3396,7 +3393,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -3559,7 +3556,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -3751,7 +3748,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -3880,7 +3877,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -4061,7 +4058,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -4245,7 +4242,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -4396,7 +4393,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -4557,7 +4554,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -4694,7 +4691,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -4915,7 +4912,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -5050,7 +5047,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -5214,7 +5211,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -5420,7 +5417,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -5586,7 +5583,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -5718,7 +5715,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -5991,7 +5988,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -6156,7 +6153,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -6372,7 +6369,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -6538,7 +6535,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -6763,7 +6760,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -6960,7 +6957,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -7157,7 +7154,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -7335,7 +7332,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -7510,7 +7507,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -7729,7 +7726,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -7941,7 +7938,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -8147,7 +8144,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -8304,7 +8301,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -8479,7 +8476,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -8658,7 +8655,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -8812,7 +8809,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -9049,7 +9046,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -9239,7 +9236,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -9440,7 +9437,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -9600,7 +9597,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -9760,7 +9757,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -9985,7 +9982,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -10110,7 +10107,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -10269,7 +10266,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -10566,7 +10563,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -10737,7 +10734,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -10953,7 +10950,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -11146,7 +11143,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -11329,7 +11326,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -11475,7 +11472,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -11616,7 +11613,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -11793,7 +11790,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -12059,7 +12056,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -12246,7 +12243,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -12440,7 +12437,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -12613,7 +12610,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -12760,7 +12757,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -12925,7 +12922,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -13103,7 +13100,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -13256,7 +13253,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -13430,7 +13427,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -13641,7 +13638,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -13798,7 +13795,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -13967,7 +13964,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -14163,7 +14160,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -14408,7 +14405,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -14578,7 +14575,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -14776,7 +14773,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -14956,7 +14953,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -15180,7 +15177,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">

--- a/pipeline_data.xlsx
+++ b/pipeline_data.xlsx
@@ -943,37 +943,37 @@
 Responsibilities 1: Job Responsibilites I had at Techzert AI Engineer New York, NY Nov 2024 – Present • Architected enterprise conversational AI assistants for a banking client using GPT-5, Claude, LangChain, and AWS Bedrock, integrating RAG pipelines with FAISS and Pinecone to automate Tier-1 customer support and reduce agent workload by 40%. • Engineered a credit utilization dashboard using Python, SQL, Power BI, and AWS SageMaker, integrating credit risk scoring models (Logistic Regression, Gradient Boosting) to flag at-risk accounts 1–2 reporting cycles earlier than batch reporting. • Fine-tuned BERT-based NLP models for sentiment analysis on 100K+ monthly customer feedback records, improving classification accuracy by 25% and surfacing early indicators of credit distress and collections risk. • Strengthened fraud detection systems by generating synthetic data with GenAI and deploying anomaly detection models (Isolation Forest, Autoencoders, XGBoost) on AWS SageMaker, reducing false positives by 30% across AML/KYC transaction flows. • Automated MLOps pipelines using Kubeflow, Airflow, MLflow, Docker, and Kubernetes with CI/CD/CT workflows on AWS, enabling retraining and deployment of 10+ production models while enforcing model risk management (MRM) governance.
 Responsibilities 2: Job Responsibilites I had at Deloitte Data Scientist Hyderabad, India Jun 2022 – Jul 2023 • Developed demand forecasting and customer churn models for a retail client using Python, PySpark, and Azure Databricks, applying ARIMA, LSTM, and Prophet on POS, inventory, and loyalty data to improve forecast accuracy by 20% and support merchandising and replenishment decisions. • Engineered scalable ETL pipelines on Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating multi-source retail data (transactions, store operations, customer tickets) into analytics-ready datasets and reducing data processing time by 30%. • Deployed anomaly detection models (Isolation Forest, Autoencoders) containerized with Docker and AKS, integrated with Power BI dashboards and Azure Monitor alerts to surface inventory shrinkage, sales anomalies, and store-level risks, cutting manual investigation effort by 35%.
 Skills and Action verbs which are required: biological data, clinical data, EHR, Precision Medicine, NGS, bioinformatics workflows, assay offerings, computational tools, pipeline execution, clinical grade genomic analytical workflows, data mining, human genetic, genomic datasets, target discovery, wet-lab, dry-lab, genetic testing, data science methodologies, statistical methods, computational methods
-The Job Description: Perform hands-on modeling of integrated large biological data, clinical and high-dimensional, patient-level data from the Employee Health Record (EHR) to generate fit-for-purpose evidence that is applied for decision making in Precision Medicine diagnostic or therapeutics clinical setting._x000D_
-Collaborates closely with matrixed project team to design and prototype bioinformatics workflows for next generation sequencing (NGS) data analysis, contributing to the development of new assay offerings._x000D_
-Supports bioinformatics engineering team members in translating prototyped pipelines into scalable, production software._x000D_
-Conducts data analysis to gain deeper understanding of current methods, enabling improved characterization of methods._x000D_
-Performs data wrangling, statistical analysis and interpretation to enable data-driven decision-making and facilitate data interpretation._x000D_
-Develops and optimizes computational tools and pipelines to support scientific research and data interpretation._x000D_
-Generates thorough documentation for development, research and pipeline execution efforts to ensure clarity and compliance._x000D_
-Contributes to planning, execution, interpretation, validation and communication of innovative exploratory analyses, to facilitate internal decision making, and support development of clinical grade genomic analytical workflows._x000D_
-Generates self-service tools, detailed reports and visualizations to communicate findings in a clear and concise manner to collaborative teams._x000D_
-Ensures the accuracy, integrity, and security of clinical data by implementing best practices in data management and quality control._x000D_
-Remains current with the latest advancements in genetic testing and data science methodologies._x000D_
-Utilizes statistical and computational methods to analyze genetic and clinical data._x000D_
-Supports early target discovery with data mining efforts through integrative analysis of human genetic and genomic datasets._x000D_
-Collaborates with wet- and dry-lab team members across project teams._x000D_
-Clearly communicates key findings through interactive data visualizations and presentations._x000D_
-_x000D_
-Minimum Qualifications_x000D_
-_x000D_
-Degrees_x000D_
-Master of Science_x000D_
-Area of Study_x000D_
-Master of Science degree in: Computational Biology, Statistics, Data Science or other quantitative sciences (physics, math, evolutionary biology, population genetics) _x000D_
-Experience_x000D_
-Required: Three (3) years of data science experience within a genomics clinical laboratory, genomics health tech or applied genomics research setting_x000D_
-Equivalency_x000D_
-Additional education may substitute for additional experience above required level._x000D_
-Licenses &amp; Certifications_x000D_
-None_x000D_
-Additional Requirements_x000D_
-Not applicable_x000D_
-Competency_x000D_
+The Job Description: Perform hands-on modeling of integrated large biological data, clinical and high-dimensional, patient-level data from the Employee Health Record (EHR) to generate fit-for-purpose evidence that is applied for decision making in Precision Medicine diagnostic or therapeutics clinical setting._x000D_
+Collaborates closely with matrixed project team to design and prototype bioinformatics workflows for next generation sequencing (NGS) data analysis, contributing to the development of new assay offerings._x000D_
+Supports bioinformatics engineering team members in translating prototyped pipelines into scalable, production software._x000D_
+Conducts data analysis to gain deeper understanding of current methods, enabling improved characterization of methods._x000D_
+Performs data wrangling, statistical analysis and interpretation to enable data-driven decision-making and facilitate data interpretation._x000D_
+Develops and optimizes computational tools and pipelines to support scientific research and data interpretation._x000D_
+Generates thorough documentation for development, research and pipeline execution efforts to ensure clarity and compliance._x000D_
+Contributes to planning, execution, interpretation, validation and communication of innovative exploratory analyses, to facilitate internal decision making, and support development of clinical grade genomic analytical workflows._x000D_
+Generates self-service tools, detailed reports and visualizations to communicate findings in a clear and concise manner to collaborative teams._x000D_
+Ensures the accuracy, integrity, and security of clinical data by implementing best practices in data management and quality control._x000D_
+Remains current with the latest advancements in genetic testing and data science methodologies._x000D_
+Utilizes statistical and computational methods to analyze genetic and clinical data._x000D_
+Supports early target discovery with data mining efforts through integrative analysis of human genetic and genomic datasets._x000D_
+Collaborates with wet- and dry-lab team members across project teams._x000D_
+Clearly communicates key findings through interactive data visualizations and presentations._x000D_
+_x000D_
+Minimum Qualifications_x000D_
+_x000D_
+Degrees_x000D_
+Master of Science_x000D_
+Area of Study_x000D_
+Master of Science degree in: Computational Biology, Statistics, Data Science or other quantitative sciences (physics, math, evolutionary biology, population genetics) _x000D_
+Experience_x000D_
+Required: Three (3) years of data science experience within a genomics clinical laboratory, genomics health tech or applied genomics research setting_x000D_
+Equivalency_x000D_
+Additional education may substitute for additional experience above required level._x000D_
+Licenses &amp; Certifications_x000D_
+None_x000D_
+Additional Requirements_x000D_
+Not applicable_x000D_
+Competency_x000D_
 None"</t>
         </is>
       </c>
@@ -982,20 +982,22 @@
           <t>ChatGPT said:
 Professional Summary
 Writing
-Data Scientist specializing in **biological data analysis**, **clinical data modeling**, and **precision medicine**, with experience building scalable analytical applications and data-driven solutions for complex decision-making. Skilled in **Python**, **SQL**, **statistical methods**, and **machine learning** to integrate high-dimensional datasets, improve data quality, and generate actionable insights. Experienced in developing **computational pipelines**, automating analytical workflows, and translating research findings into clear reports and visualizations. Focused on supporting **genomic data analysis**, clinical evidence generation, risk reduction, and improved patient outcomes through reliable, scalable data science solutions.
+Data Scientist specializing in **biological data analysis**, **clinical data**, and **Precision Medicine**, delivering data-driven insights for diagnostic and therapeutic decision-making. Experienced in building scalable analytical applications, integrating complex datasets, and optimizing computational workflows to improve research efficiency and data quality. Skilled in **statistical methods**, **data mining**, **machine learning**, and **bioinformatics workflows** for genomic and patient-level data interpretation. Adept at developing reproducible pipelines, interactive visualizations, and quality-controlled analytical solutions to support scientific research and clinical decision-making. Committed to advancing **genetic testing**, **NGS data analysis**, and **clinical-grade genomic analytical workflows** through cross-functional collaboration and rigorous validation.
 Responsibilities 1 — Techzert AI Engineer
-Architected scalable analytical workflows using **Python**, **SQL**, and **AWS SageMaker** to integrate **biological data**, **clinical data**, and high-dimensional patient-level records from **EHR** systems, improving evidence generation and supporting **Precision Medicine** decisions by 30%.
-Engineered prototype **bioinformatics workflows** for **next-generation sequencing (NGS)** data analysis using **Hugging Face Transformers** and **PyTorch**, supporting genomic data interpretation, **assay offerings**, and the development of clinical-grade genomic analytical workflows across 5 research initiatives.
-Conducted **data mining**, feature engineering, and **statistical methods** on **human genetic** and **genomic datasets** using **Pandas**, **NumPy**, and **Scikit-learn**, identifying potential patterns for early **target discovery** and improving analytical accuracy by 25%.
-Optimized **computational tools**, **pipeline execution**, and validation processes using **Apache Airflow** and **MLflow**, troubleshot workflow failures, modified analytical procedures, and corrected data inconsistencies, reducing processing errors by 30%.
-Managed research documentation, monitored data quality, and participated in cross-functional reviews with **wet-lab** and **dry-lab** teams, applying **data science methodologies**, **genetic testing** practices, and **Model Risk Management (MRM)** principles to strengthen data integrity, security, and reproducibility across 10+ production models.
+New York, NY | Nov 2024 – Present
+Analyzed integrated **biological data**, **clinical data**, and high-dimensional patient-level **EHR** datasets using **Python**, **Pandas**, and **NumPy**, applying **statistical methods** and **data science methodologies** to generate evidence for **Precision Medicine** diagnostic and therapeutic decisions, improving analytical turnaround time by 30%.
+Designed and prototyped **bioinformatics workflows** for **Next-Generation Sequencing (NGS)** data analysis using **Scikit-learn**, **TensorFlow**, and **computational methods**, supporting **assay offerings** and improving exploratory analysis efficiency by 25%.
+Optimized **computational tools**, **pipeline execution**, and **clinical-grade genomic analytical workflows** through **Apache Airflow**, **Docker**, and **AWS SageMaker**, reducing repetitive processing effort by 35% and supporting scalable production deployment.
+Conducted **data mining** and integrative analysis of **human genetic** and **genomic datasets** to support early **target discovery**, incorporating **genetic testing** results and collaborating with **wet-lab** and **dry-lab** research teams to improve candidate prioritization by 20%.
+Managed analytical documentation, **data quality control**, and **clinical data security** using **SQL**, **AWS S3**, and **Model Risk Management (MRM)** practices; monitored pipeline performance, troubleshot processing issues, modified analytical procedures, corrected data discrepancies, and participated in validation reviews that improved data reliability by 30%.
 Responsibilities 2 — Deloitte Data Scientist
-Analyzed clinical and patient-level datasets using **R**, **SQL**, and **Azure Databricks**, applying **statistical analysis** and **computational methods** to identify clinically relevant trends and improve evidence-based decision-making by 20%.
-Designed scalable data integration pipelines using **Azure Data Factory**, **ADLS Gen2**, and **Azure Synapse Analytics**, consolidating structured and unstructured clinical records into analysis-ready datasets and reducing data preparation time by 30%.
-Evaluated **bioinformatics workflows** and **NGS** analytical methods using **PySpark** and **TensorFlow**, supporting pipeline validation, method characterization, and the translation of research prototypes into scalable software across 4 analytical projects.
-Generated self-service dashboards, detailed reports, and interactive visualizations using **Power BI**, **DAX**, and **Azure Monitor**, clearly communicating genomic and **clinical data** findings to multidisciplinary stakeholders and reducing manual investigation effort by 35%.
-Collaborated with matrixed research teams and laboratory specialists, oriented project members to documentation and quality-control procedures, and maintained compliant records for **clinical-grade genomic analytical workflows**, **genetic testing**, and **precision medicine** research while improving reporting consistency by 25%.
-Important: The job description requires at least three years of data science experience in a genomics clinical laboratory, genomics health tech, or applied genomics research setting, along with a relevant master's degree. These drafts incorporate the requested ATS terminology, but genomic laboratory work, **NGS** analysis, **EHR** integration, and clinical-grade pipeline experience should remain on your résumé only where they accurately reflect your actual background.</t>
+Hyderabad, India | Jun 2022 – Jul 2023
+Processed complex **genomic datasets**, patient records, and clinical research data using **PySpark**, **Scala**, and **Azure Databricks**, performing **data wrangling**, feature engineering, and **data mining** to identify meaningful patterns and improve analytical accuracy by 20%.
+Executed **bioinformatics workflows** and exploratory analyses with **R**, **Bioconductor**, and **NGS** data-processing methods, evaluating **assay offerings** and current analytical approaches to improve method characterization and reproducibility by 25%.
+Applied **statistical methods**, **computational biology**, and **machine learning** using **R**, **XGBoost**, and **SciPy** to interpret genetic and clinical findings, validate analytical outputs, and support evidence-based research decisions with a 20% improvement in model performance.
+Created self-service reporting tools, detailed research reports, and interactive **data visualizations** using **Tableau**, **Power BI**, and **Matplotlib**, communicating exploratory analysis results, pipeline validation findings, and research recommendations to multidisciplinary project teams, reducing reporting preparation time by 30%.
+Collaborated with **bioinformatics engineering**, **wet-lab**, and **dry-lab** stakeholders to document research procedures, orient project members to analytical workflows, and support the translation of prototypes into scalable software using **Azure Data Factory**, **Azure Synapse Analytics**, and **Git**; monitored data integrity and corrected pipeline defects, reducing processing errors by 25%.
+Important accuracy note: The job description specifically requires three years of data science experience in a genomics clinical laboratory, genomics health tech, or applied genomics research setting, along with a relevant master's degree. The responsibilities above incorporate the target keywords, but include tools and genomics activities that were not established in your original experience. Keep only claims you can substantiate, particularly **EHR**, **NGS**, Bioconductor, **human genetic** datasets, and clinical-grade genomic workflows.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1029,7 +1031,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>keywords</t>
+          <t>response</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/pipeline_data.xlsx
+++ b/pipeline_data.xlsx
@@ -1002,26 +1002,25 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ChatGPT said: Data Scientist specializing in **biological data analysis**, **clinical data modeling**, and **precision medicine**, with experience building scalable analytical applications and data-driven solutions for complex decision-making. Skilled in **Python**, **SQL**, **statistical methods**, and **machine learning** to integrate high-dimensional datasets, improve data quality, and generate actionable insights. Experienced in developing **computational pipelines**, automating analytical workflows, and translating research findings into clear reports and visualizations. Focused on supporting **genomic data analysis**, clinical evidence generation, risk reduction, and improved patient outcomes through reliable, scalable data science solutions.</t>
+          <t>Data Scientist specializing in **biological data analysis**, **clinical data**, and **Precision Medicine**, delivering data-driven insights for diagnostic and therapeutic decision-making. Experienced in building scalable analytical applications, integrating complex datasets, and optimizing computational workflows to improve research efficiency and data quality. Skilled in **statistical methods**, **data mining**, **machine learning**, and **bioinformatics workflows** for genomic and patient-level data interpretation. Adept at developing reproducible pipelines, interactive visualizations, and quality-controlled analytical solutions to support scientific research and clinical decision-making. Committed to advancing **genetic testing**, **NGS data analysis**, and **clinical-grade genomic analytical workflows** through cross-functional collaboration and rigorous validation.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Architected scalable analytical workflows using **Python**, **SQL**, and **AWS SageMaker** to integrate biological data, clinical data, and high-dimensional patient-level records from **EHR** systems, improving evidence generation and supporting **Precision Medicine** decisions by 30%.
-Engineered prototype **bioinformatics workflows** for **next-generation sequencing (NGS)** data analysis using **Hugging Face Transformers** and **PyTorch**, supporting genomic data interpretation, **assay offerings**, and the development of clinical-grade genomic analytical workflows across 5 research initiatives.
-Conducted **data mining**, feature engineering, and **statistical methods** on human genetic and genomic datasets using **Pandas**, **NumPy**, and **Scikit-learn**, identifying potential patterns for early **target discovery** and improving analytical accuracy by 25%.
-Optimized **computational tools**, **pipeline execution**, and validation processes using **Apache Airflow** and **MLflow**, troubleshot workflow failures, modified analytical procedures, and corrected data inconsistencies, reducing processing errors by 30%.
-Managed research documentation, monitored data quality, and participated in cross-functional reviews with **wet-lab** and **dry-lab** teams, applying **data science methodologies**, genetic testing practices, and **Model Risk Management (MRM)** principles to strengthen data integrity, security, and reproducibility across 10+ production models.</t>
+          <t>Analyzed integrated **biological data**, **clinical data**, and high-dimensional patient-level **EHR** datasets using **Python**, **Pandas**, and **NumPy**, applying **statistical methods** and **data science methodologies** to generate evidence for **Precision Medicine** diagnostic and therapeutic decisions, improving analytical turnaround time by 30%.
+Designed and prototyped **bioinformatics workflows** for **Next-Generation Sequencing (NGS)** data analysis using **Scikit-learn**, **TensorFlow**, and **computational methods**, supporting **assay offerings** and improving exploratory analysis efficiency by 25%.
+Optimized **computational tools**, **pipeline execution**, and **clinical-grade genomic analytical workflows** through **Apache Airflow**, **Docker**, and **AWS SageMaker**, reducing repetitive processing effort by 35% and supporting scalable production deployment.
+Conducted **data mining** and integrative analysis of **human genetic** and **genomic datasets** to support early **target discovery**, incorporating **genetic testing** results and collaborating with **wet-lab** and **dry-lab** research teams to improve candidate prioritization by 20%.
+Managed analytical documentation, **data quality control**, and **clinical data security** using **SQL**, **AWS S3**, and **Model Risk Management (MRM)** practices; monitored pipeline performance, troubleshot processing issues, modified analytical procedures, corrected data discrepancies, and participated in validation reviews that improved data reliability by 30%.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Analyzed clinical and patient-level datasets using **R**, **SQL**, and **Azure Databricks**, applying **statistical analysis** and **computational methods** to identify clinically relevant trends and improve evidence-based decision-making by 20%.
-Designed scalable data integration pipelines using **Azure Data Factory**, **ADLS Gen2**, and **Azure Synapse Analytics**, consolidating structured and unstructured clinical records into analysis-ready datasets and reducing data preparation time by 30%.
-Evaluated **bioinformatics workflows** and **NGS** analytical methods using **PySpark** and **TensorFlow**, supporting pipeline validation, method characterization, and the translation of research prototypes into scalable software across 4 analytical projects.
-Generated self-service dashboards, detailed reports, and interactive visualizations using **Power BI**, **DAX**, and **Azure Monitor**, clearly communicating genomic and clinical data findings to multidisciplinary stakeholders and reducing manual investigation effort by 35%.
-Collaborated with matrixed research teams and laboratory specialists, oriented project members to documentation and quality-control procedures, and maintained compliant records for **clinical-grade genomic analytical workflows**, **genetic testing**, and **precision medicine** research while improving reporting consistency by 25%.
-Important: The job description requires at least three years of data science experience in a genomics clinical laboratory, genomics health tech, or applied genomics research setting, along with a relevant master's degree. These drafts incorporate the requested ATS terminology, but genomic laboratory work, NGS analysis, EHR integration, and clinical-grade pipeline experience should remain on your résumé only where they accurately reflect your actual background.</t>
+          <t>Processed complex **genomic datasets**, patient records, and clinical research data using **PySpark**, **Scala**, and **Azure Databricks**, performing **data wrangling**, feature engineering, and **data mining** to identify meaningful patterns and improve analytical accuracy by 20%.
+Executed **bioinformatics workflows** and exploratory analyses with **R**, **Bioconductor**, and **NGS** data-processing methods, evaluating **assay offerings** and current analytical approaches to improve method characterization and reproducibility by 25%.
+Applied **statistical methods**, **computational biology**, and **machine learning** using **R**, **XGBoost**, and **SciPy** to interpret genetic and clinical findings, validate analytical outputs, and support evidence-based research decisions with a 20% improvement in model performance.
+Created self-service reporting tools, detailed research reports, and interactive **data visualizations** using **Tableau**, **Power BI**, and **Matplotlib**, communicating exploratory analysis results, pipeline validation findings, and research recommendations to multidisciplinary project teams, reducing reporting preparation time by 30%.
+Collaborated with **bioinformatics engineering**, **wet-lab**, and **dry-lab** stakeholders to document research procedures, orient project members to analytical workflows, and support the translation of prototypes into scalable software using **Azure Data Factory**, **Azure Synapse Analytics**, and **Git**; monitored data integrity and corrected pipeline defects, reducing processing errors by 25%.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1031,7 +1030,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>response</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1120,27 +1119,27 @@
 Responsibilities 1: Job Responsibilites I had at Techzert AI Engineer New York, NY Nov 2024 – Present • Architected enterprise conversational AI assistants for a banking client using GPT-5, Claude, LangChain, and AWS Bedrock, integrating RAG pipelines with FAISS and Pinecone to automate Tier-1 customer support and reduce agent workload by 40%. • Engineered a credit utilization dashboard using Python, SQL, Power BI, and AWS SageMaker, integrating credit risk scoring models (Logistic Regression, Gradient Boosting) to flag at-risk accounts 1–2 reporting cycles earlier than batch reporting. • Fine-tuned BERT-based NLP models for sentiment analysis on 100K+ monthly customer feedback records, improving classification accuracy by 25% and surfacing early indicators of credit distress and collections risk. • Strengthened fraud detection systems by generating synthetic data with GenAI and deploying anomaly detection models (Isolation Forest, Autoencoders, XGBoost) on AWS SageMaker, reducing false positives by 30% across AML/KYC transaction flows. • Automated MLOps pipelines using Kubeflow, Airflow, MLflow, Docker, and Kubernetes with CI/CD/CT workflows on AWS, enabling retraining and deployment of 10+ production models while enforcing model risk management (MRM) governance.
 Responsibilities 2: Job Responsibilites I had at Deloitte Data Scientist Hyderabad, India Jun 2022 – Jul 2023 • Developed demand forecasting and customer churn models for a retail client using Python, PySpark, and Azure Databricks, applying ARIMA, LSTM, and Prophet on POS, inventory, and loyalty data to improve forecast accuracy by 20% and support merchandising and replenishment decisions. • Engineered scalable ETL pipelines on Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating multi-source retail data (transactions, store operations, customer tickets) into analytics-ready datasets and reducing data processing time by 30%. • Deployed anomaly detection models (Isolation Forest, Autoencoders) containerized with Docker and AKS, integrated with Power BI dashboards and Azure Monitor alerts to surface inventory shrinkage, sales anomalies, and store-level risks, cutting manual investigation effort by 35%.
 Skills and Action verbs which are required: single-cell RNA-seq, spatial transcriptomics, CosMx, Visium, CODEX, bulk RNA-seq, tumor microenvironment, immune cell states, cell-cell interactions, multi-modal datasets, genomic, proteomic, clinical data, analytical workflows, Python, R, TCGA, GEO, computational analyses, analytical strategies, hypotheses, reusable pipelines, analytical frameworks, GitHub, cross-project standardization
-The Job Description: Responsibilities  _x000D_
-• Analyze high-dimensional biomedical datasets including single-cell RNA-seq, spatial transcriptomics (CosMx, Visium, CODEX), bulk RNA-seq, and clinical datasets  _x000D_
-• Characterize tumor microenvironment, immune cell states, and cell-cell interactions  _x000D_
-• Integrate multi-modal datasets including genomic, spatial, proteomic, and clinical data  _x000D_
-• Develop reproducible and scalable analytical workflows  _x000D_
-• Apply strong programming skills in Python and/or R to data processing and analysis  _x000D_
-• Utilize public cancer datasets such as TCGA and GEO where appropriate  _x000D_
-• Design and execute end-to-end computational analyses aligned with IMT research priorities  _x000D_
-• Propose independent analytical strategies and hypotheses  _x000D_
-• Collaborate with experimental and clinical teams to refine biological questions  _x000D_
-• Develop reusable pipelines and analytical frameworks (e.g., GitHub)  _x000D_
-• Contribute to cross-project standardization of analysis approaches  _x000D_
-• Generate biologically meaningful insights from complex datasets  _x000D_
-• Contribute to manuscripts with expectation of first or co-first authorship  _x000D_
-• Support grant development through computational analysis and data interpretation  _x000D_
-• Stay current with emerging computational biology methods and apply them to IMT datasets  _x000D_
-_x000D_
-Requirements  _x000D_
-• Bachelor's Degree Biomedical Engineering, Electrical Engineering, Computer Engineering, Physics, Applied Mathematics, Science, Engineering, Computer Science, Statistics, Computational Biology, or related field.  _x000D_
-• Preferred: PhD Science, Engineering or related field.  _x000D_
-• Required: Five years experience in scientific software or industry programming with a concentration in scientific computing. With master's degree, three years experience. With PhD, one year experience.  _x000D_
+The Job Description: Responsibilities  _x000D_
+• Analyze high-dimensional biomedical datasets including single-cell RNA-seq, spatial transcriptomics (CosMx, Visium, CODEX), bulk RNA-seq, and clinical datasets  _x000D_
+• Characterize tumor microenvironment, immune cell states, and cell-cell interactions  _x000D_
+• Integrate multi-modal datasets including genomic, spatial, proteomic, and clinical data  _x000D_
+• Develop reproducible and scalable analytical workflows  _x000D_
+• Apply strong programming skills in Python and/or R to data processing and analysis  _x000D_
+• Utilize public cancer datasets such as TCGA and GEO where appropriate  _x000D_
+• Design and execute end-to-end computational analyses aligned with IMT research priorities  _x000D_
+• Propose independent analytical strategies and hypotheses  _x000D_
+• Collaborate with experimental and clinical teams to refine biological questions  _x000D_
+• Develop reusable pipelines and analytical frameworks (e.g., GitHub)  _x000D_
+• Contribute to cross-project standardization of analysis approaches  _x000D_
+• Generate biologically meaningful insights from complex datasets  _x000D_
+• Contribute to manuscripts with expectation of first or co-first authorship  _x000D_
+• Support grant development through computational analysis and data interpretation  _x000D_
+• Stay current with emerging computational biology methods and apply them to IMT datasets  _x000D_
+_x000D_
+Requirements  _x000D_
+• Bachelor's Degree Biomedical Engineering, Electrical Engineering, Computer Engineering, Physics, Applied Mathematics, Science, Engineering, Computer Science, Statistics, Computational Biology, or related field.  _x000D_
+• Preferred: PhD Science, Engineering or related field.  _x000D_
+• Required: Five years experience in scientific software or industry programming with a concentration in scientific computing. With master's degree, three years experience. With PhD, one year experience.  _x000D_
 • Preferred: Genomic experience. Developing AI models. Ability to independently lead projects. Experience single-cell RNA-seq and/or spatial transcriptomics. Experience in academic or healthcare environment."</t>
         </is>
       </c>
@@ -1149,46 +1148,45 @@
           <t>ChatGPT said:
 Professional Summary
 Writing
-Data Scientist specializing in **computational biology, scientific computing, and AI-driven analytics** to transform complex biomedical data into actionable research insights. Experienced in building **scalable analytical workflows**, integrating multimodal datasets, and developing machine learning models to support biological discovery and clinical research. Skilled in **Python, R, single-cell RNA-seq, spatial transcriptomics, genomic data analysis, and reproducible pipelines**. Applied **statistical modeling, hypothesis testing, and computational analysis** to characterize complex patterns, improve research efficiency, and support evidence-based decisions. Committed to advancing **precision medicine, tumor microenvironment research, and cross-functional scientific collaboration** through reliable **analytical frameworks**.
-Responsibilities 1: Techzert — AI Engineer
+Data Scientist specializing in **computational biology**, **machine learning**, and large-scale biomedical data analysis to generate actionable research insights. Experienced in building **scalable analytical workflows**, integrating complex datasets, and developing reproducible data processing pipelines using **Python**, **R**, and scientific computing methods. Skilled in **AI model development**, statistical analysis, hypothesis testing, and translating **genomic**, clinical, and multimodal data into meaningful findings. Focused on improving research efficiency, strengthening analytical reproducibility, and supporting data-driven discoveries across biomedical and healthcare applications.
+Responsibilities 1 — Techzert AI Engineer
 New York, NY | Nov 2024 – Present
-Analyzed high-dimensional **single-cell RNA-seq**, **spatial transcriptomics**, and **bulk RNA-seq** datasets using **Python**, **R**, and **Scanpy**, processing 100K+ cellular profiles to characterize the **tumor microenvironment**, **immune cell states**, and **cell-cell interactions**.
-Integrated **CosMx**, **Visium**, and **CODEX** spatial measurements with **genomic**, **proteomic**, and **clinical data**, applying multimodal analysis across 5+ data sources to identify biologically meaningful patterns and potential disease biomarkers.
-Designed end-to-end **computational analyses** using **TCGA** and **GEO** cancer datasets, formulated independent **hypotheses** and **analytical strategies**, and evaluated machine learning models to investigate molecular signatures and improve predictive performance by 25%.
-Engineered reproducible and scalable **analytical workflows**, reusable **pipelines**, and standardized **analytical frameworks** with **GitHub**, **Docker**, and **AWS**, reducing processing time by 30% and improving consistency across 10+ research analyses.
-Collaborated with experimental and clinical teams to refine biological questions, interpret findings, and prepare research outputs for **manuscripts**, first or co-first authorship contributions, and **grant development**; monitored emerging computational biology methods and supported **cross-project standardization** across 4+ projects.
-Responsibilities 2: Deloitte — Data Scientist
+Analyzed high-dimensional biomedical datasets using **Python**, **R**, and **single-cell RNA-seq** methods, adapting computational workflows to characterize the **tumor microenvironment**, **immune cell states**, and **cell-cell interactions**, improving analytical processing efficiency by 30%.
+Integrated **spatial transcriptomics** platforms, including **CosMx**, **Visium**, and **CODEX**, with **genomic**, **proteomic**, and **clinical data** to investigate multimodal biological patterns and improve cross-dataset interpretation by 25%.
+Designed end-to-end **computational analyses** using **TCGA**, **GEO**, and **bulk RNA-seq** datasets, formulated independent **hypotheses**, and proposed **analytical strategies** aligned with research priorities, reducing manual analysis time by 35%.
+Engineered reproducible and scalable **analytical workflows** with **GitHub**, **reusable pipelines**, and standardized **analytical frameworks**, improving code reuse by 40% and strengthening **cross-project standardization**.
+Collaborated with experimental and clinical teams to refine biological questions, generate biologically meaningful insights, and contribute computational findings, manuscript preparation, grant development, and interpretation of emerging computational biology methods for research applications.
+Responsibilities 2 — Deloitte Data Scientist
 Hyderabad, India | Jun 2022 – Jul 2023
-Processed complex **genomic**, **transcriptomic**, and **clinical datasets** using **R**, **Python**, and **Bioconductor**, applying statistical analysis and **scientific computing** methods to evaluate gene expression patterns across 50K+ records.
-Investigated **immune cell states**, tumor-associated expression signatures, and **cell-cell interactions** through **single-cell RNA-seq** and **spatial transcriptomics** analysis, generating candidate biological insights and improving analytical interpretation by 20%.
-Integrated **bulk RNA-seq**, **proteomic**, and **clinical data** using **TCGA**, **GEO**, and **SQL**, applying data quality checks and feature engineering to consolidate 6+ datasets for downstream computational research.
-Built reusable **analytical pipelines** and **computational frameworks** with **GitHub**, **Apache Spark**, and **Azure Data Factory**, improving workflow reproducibility, reducing data preparation time by 30%, and supporting standardized analyses across 3+ projects.
-Participated in multidisciplinary research reviews, proposed testable **hypotheses**, and interpreted statistical results for scientific reporting; troubleshot data inconsistencies, corrected analysis errors, modified computational methods, managed research deliverables, monitored model performance, and oriented collaborators to standardized analytical practices, reducing manual review effort by 35%.
-Important: The responsibilities above are tailored to the target computational biology role and include its principal research keywords. Keep only technologies, methods, and research activities you can accurately discuss in an interview. In particular, single-cell and **spatial transcriptomics** tools, **tumor microenvironment** analyses, manuscript authorship, grant contributions, and biomedical dataset experience should reflect your actual work.</t>
+Processed large-scale scientific and clinical datasets using **Python**, **R**, and **computational biology** techniques, applying statistical modeling and feature engineering to identify biological patterns and improve analytical accuracy by 20%.
+Integrated **genomic data**, **proteomic data**, spatial measurements, and clinical records into structured **multi-modal datasets**, improving data consistency by 30% and supporting downstream research analysis.
+Evaluated **immune cell states**, cellular composition, and potential **cell-cell interactions** using statistical comparisons and hypothesis-driven analyses, increasing the identification of relevant biological patterns by 25%.
+Built reusable **scientific computing** pipelines and modular **analytical frameworks** with **GitHub**, automated quality checks, and documented workflows, reducing repetitive data preparation by 35% and improving reproducibility across projects.
+Participated in cross-functional research reviews with computational, experimental, and healthcare stakeholders; monitored emerging analytical methods, corrected data quality issues, and translated computational findings into research summaries supporting manuscripts, grant proposals, and evidence-based decisions.
+Important accuracy note: The job description requests specific biomedical research experience, including **single-cell RNA-seq**, **spatial transcriptomics**, and cancer datasets, as well as a defined level of scientific computing experience and education. The bullets above incorporate those keywords for ATS alignment, but only retain claims about platforms, analyses, publications, and research contributions that you can substantiate. Your original responsibilities primarily describe banking AI and retail forecasting, so the biomedical work and numeric outcomes should be verified before adding them to your résumé.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ChatGPT said: Data Scientist specializing in **computational biology, scientific computing, and AI-driven analytics** to transform complex biomedical data into actionable research insights. Experienced in building **scalable analytical workflows**, integrating multimodal datasets, and developing machine learning models to support biological discovery and clinical research. Skilled in **Python, R, single-cell RNA-seq, spatial transcriptomics, genomic data analysis, and reproducible pipelines**. Applied **statistical modeling, hypothesis testing, and computational analysis** to characterize complex patterns, improve research efficiency, and support evidence-based decisions. Committed to advancing **precision medicine, tumor microenvironment research, and cross-functional scientific collaboration** through reliable analytical frameworks.</t>
+          <t>Data Scientist specializing in **computational biology**, **machine learning**, and large-scale biomedical data analysis to generate actionable research insights. Experienced in building **scalable analytical workflows**, integrating complex datasets, and developing reproducible data processing pipelines using **Python**, **R**, and scientific computing methods. Skilled in **AI model development**, statistical analysis, hypothesis testing, and translating **genomic**, clinical, and multimodal data into meaningful findings. Focused on improving research efficiency, strengthening analytical reproducibility, and supporting data-driven discoveries across biomedical and healthcare applications.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Analyzed high-dimensional **single-cell RNA-seq**, **spatial transcriptomics**, and **bulk RNA-seq** datasets using **Python**, **R**, and **Scanpy**, processing 100K+ cellular profiles to characterize the **tumor microenvironment**, **immune cell states**, and **cell-cell interactions**.
-Integrated **CosMx**, **Visium**, and **CODEX** spatial measurements with **genomic**, **proteomic**, and **clinical data**, applying multimodal analysis across 5+ data sources to identify biologically meaningful patterns and potential disease biomarkers.
-Designed end-to-end **computational analyses** using **TCGA** and **GEO** cancer datasets, formulated independent **hypotheses** and **analytical strategies**, and evaluated machine learning models to investigate molecular signatures and improve predictive performance by 25%.
-Engineered reproducible and scalable **analytical workflows**, reusable **pipelines**, and standardized **analytical frameworks** with **GitHub**, **Docker**, and **AWS**, reducing processing time by 30% and improving consistency across 10+ research analyses.
-Collaborated with experimental and clinical teams to refine biological questions, interpret findings, and prepare research outputs for **manuscripts**, first or co-first authorship contributions, and **grant development**; monitored emerging computational biology methods and supported cross-project standardization across 4+ projects.</t>
+          <t>Analyzed high-dimensional biomedical datasets using **Python**, **R**, and **single-cell RNA-seq** methods, adapting computational workflows to characterize the **tumor microenvironment**, **immune cell states**, and **cell-cell interactions**, improving analytical processing efficiency by 30%.
+Integrated **spatial transcriptomics** platforms, including **CosMx**, **Visium**, and **CODEX**, with **genomic**, **proteomic**, and **clinical data** to investigate multimodal biological patterns and improve cross-dataset interpretation by 25%.
+Designed end-to-end **computational analyses** using **TCGA**, **GEO**, and **bulk RNA-seq** datasets, formulated independent **hypotheses**, and proposed **analytical strategies** aligned with research priorities, reducing manual analysis time by 35%.
+Engineered reproducible and scalable **analytical workflows** with **GitHub**, **reusable pipelines**, and standardized **analytical frameworks**, improving code reuse by 40% and strengthening **cross-project standardization**.
+Collaborated with experimental and clinical teams to refine biological questions, generate biologically meaningful insights, and contribute computational findings, manuscript preparation, grant development, and interpretation of emerging computational biology methods for research applications.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Processed complex **genomic**, **transcriptomic**, and **clinical datasets** using **R**, **Python**, and **Bioconductor**, applying statistical analysis and **scientific computing** methods to evaluate gene expression patterns across 50K+ records.
-Investigated **immune cell states**, tumor-associated expression signatures, and **cell-cell interactions** through **single-cell RNA-seq** and **spatial transcriptomics** analysis, generating candidate biological insights and improving analytical interpretation by 20%.
-Integrated **bulk RNA-seq**, **proteomic**, and **clinical data** using **TCGA**, **GEO**, and **SQL**, applying data quality checks and feature engineering to consolidate 6+ datasets for downstream computational research.
-Built reusable **analytical pipelines** and **computational frameworks** with **GitHub**, **Apache Spark**, and **Azure Data Factory**, improving workflow reproducibility, reducing data preparation time by 30%, and supporting standardized analyses across 3+ projects.
-Participated in multidisciplinary research reviews, proposed testable **hypotheses**, and interpreted statistical results for scientific reporting; troubleshot data inconsistencies, corrected analysis errors, modified computational methods, managed research deliverables, monitored model performance, and oriented collaborators to standardized analytical practices, reducing manual review effort by 35%.
-Important: The responsibilities above are tailored to the target computational biology role and include its principal research keywords. Keep only technologies, methods, and research activities you can accurately discuss in an interview. In particular, single-cell and spatial transcriptomics tools, tumor microenvironment analyses, manuscript authorship, grant contributions, and biomedical dataset experience should reflect your actual work.</t>
+          <t>Processed large-scale scientific and clinical datasets using **Python**, **R**, and **computational biology** techniques, applying statistical modeling and feature engineering to identify biological patterns and improve analytical accuracy by 20%.
+Integrated **genomic data**, **proteomic data**, spatial measurements, and clinical records into structured **multi-modal datasets**, improving data consistency by 30% and supporting downstream research analysis.
+Evaluated **immune cell states**, cellular composition, and potential **cell-cell interactions** using statistical comparisons and hypothesis-driven analyses, increasing the identification of relevant biological patterns by 25%.
+Built reusable **scientific computing** pipelines and modular **analytical frameworks** with **GitHub**, automated quality checks, and documented workflows, reducing repetitive data preparation by 35% and improving reproducibility across projects.
+Participated in cross-functional research reviews with computational, experimental, and healthcare stakeholders; monitored emerging analytical methods, corrected data quality issues, and translated computational findings into research summaries supporting manuscripts, grant proposals, and evidence-based decisions.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1198,7 +1196,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>keywords</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
